--- a/outputs/piplio-import/Piplio-Word-Import-Live.xlsx
+++ b/outputs/piplio-import/Piplio-Word-Import-Live.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aistea/PhpstormProjects/portfolio-ais/packages/piplio_backend/outputs/piplio-import/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467BF4B8-CA22-A046-9947-D345FF21ADE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Import" sheetId="1" r:id="rId4"/>
-    <sheet name="Uebersicht" sheetId="2" r:id="rId5"/>
-    <sheet name="Hinweise" sheetId="3" r:id="rId6"/>
+    <sheet name="Import" sheetId="1" r:id="rId1"/>
+    <sheet name="Uebersicht" sheetId="2" r:id="rId2"/>
+    <sheet name="Hinweise" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Import'!$A$1:$Q$370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Import!$A$1:$Q$370</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="503">
   <si>
     <t>topic</t>
   </si>
@@ -1137,9 +1143,6 @@
     <t>u</t>
   </si>
   <si>
-    <t>H__user</t>
-  </si>
-  <si>
     <t>eu,au</t>
   </si>
   <si>
@@ -1528,49 +1531,47 @@
   </si>
   <si>
     <t>tense_when, tense_form</t>
+  </si>
+  <si>
+    <t>H__ser</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1614,28 +1615,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1925,33 +1941,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Q400"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q370"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="30" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12" customWidth="true" style="0"/>
-    <col min="5" max="5" width="18" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12" customWidth="true" style="0"/>
-    <col min="7" max="7" width="22" customWidth="true" style="0"/>
-    <col min="8" max="8" width="28" customWidth="true" style="0"/>
-    <col min="9" max="9" width="28" customWidth="true" style="0"/>
-    <col min="10" max="10" width="28" customWidth="true" style="0"/>
-    <col min="11" max="11" width="18" customWidth="true" style="0"/>
-    <col min="12" max="12" width="34" customWidth="true" style="0"/>
-    <col min="13" max="13" width="18" customWidth="true" style="0"/>
-    <col min="14" max="14" width="18" customWidth="true" style="0"/>
-    <col min="15" max="15" width="14" customWidth="true" style="0"/>
-    <col min="16" max="16" width="16" customWidth="true" style="0"/>
-    <col min="17" max="17" width="10" customWidth="true" style="0"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" customHeight="1" ht="24">
+    <row r="1" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2004,7 +2014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -2033,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -2062,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -2091,7 +2101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2120,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2149,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2178,7 +2188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2207,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -2236,7 +2246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -2265,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2294,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -2323,7 +2333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -2352,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -2381,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -2410,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -2439,7 +2449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -2468,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -2497,7 +2507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
@@ -2526,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -2555,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -2584,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
@@ -2642,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -2671,7 +2681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>17</v>
       </c>
@@ -2700,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -2729,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -2758,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
@@ -2787,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -2816,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
@@ -2845,7 +2855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -2874,7 +2884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
@@ -2903,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
@@ -2932,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>17</v>
       </c>
@@ -2961,7 +2971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
@@ -2990,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>17</v>
       </c>
@@ -3019,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>17</v>
       </c>
@@ -3048,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>17</v>
       </c>
@@ -3077,7 +3087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>17</v>
       </c>
@@ -3106,7 +3116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
@@ -3135,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>17</v>
       </c>
@@ -3164,7 +3174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>17</v>
       </c>
@@ -3193,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>17</v>
       </c>
@@ -3222,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>17</v>
       </c>
@@ -3251,7 +3261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>17</v>
       </c>
@@ -3280,7 +3290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>17</v>
       </c>
@@ -3309,7 +3319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>17</v>
       </c>
@@ -3338,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>17</v>
       </c>
@@ -3367,7 +3377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -3396,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
@@ -3425,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>17</v>
       </c>
@@ -3454,7 +3464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>17</v>
       </c>
@@ -3483,7 +3493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>17</v>
       </c>
@@ -3512,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>17</v>
       </c>
@@ -3541,7 +3551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>17</v>
       </c>
@@ -3570,7 +3580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>17</v>
       </c>
@@ -3599,7 +3609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>17</v>
       </c>
@@ -3628,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>17</v>
       </c>
@@ -3657,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>17</v>
       </c>
@@ -3686,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>17</v>
       </c>
@@ -3715,7 +3725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>17</v>
       </c>
@@ -3744,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>17</v>
       </c>
@@ -3773,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>17</v>
       </c>
@@ -3802,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>17</v>
       </c>
@@ -3831,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>17</v>
       </c>
@@ -3860,7 +3870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>17</v>
       </c>
@@ -3889,7 +3899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -3918,7 +3928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>17</v>
       </c>
@@ -3947,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>17</v>
       </c>
@@ -3976,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>17</v>
       </c>
@@ -4005,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>17</v>
       </c>
@@ -4034,7 +4044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>17</v>
       </c>
@@ -4063,7 +4073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>17</v>
       </c>
@@ -4092,7 +4102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:17">
+    <row r="74" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>17</v>
       </c>
@@ -4121,7 +4131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
+    <row r="75" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>17</v>
       </c>
@@ -4150,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:17">
+    <row r="76" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>17</v>
       </c>
@@ -4179,7 +4189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:17">
+    <row r="77" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>17</v>
       </c>
@@ -4208,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>17</v>
       </c>
@@ -4237,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:17">
+    <row r="79" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>17</v>
       </c>
@@ -4266,7 +4276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
+    <row r="80" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>17</v>
       </c>
@@ -4295,7 +4305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>17</v>
       </c>
@@ -4324,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:17">
+    <row r="82" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>17</v>
       </c>
@@ -4353,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>17</v>
       </c>
@@ -4382,7 +4392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>17</v>
       </c>
@@ -4411,7 +4421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:17">
+    <row r="85" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>17</v>
       </c>
@@ -4440,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>17</v>
       </c>
@@ -4469,7 +4479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:17">
+    <row r="87" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>17</v>
       </c>
@@ -4498,7 +4508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>17</v>
       </c>
@@ -4527,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>17</v>
       </c>
@@ -4556,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>17</v>
       </c>
@@ -4585,7 +4595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>17</v>
       </c>
@@ -4614,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:17">
+    <row r="92" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>17</v>
       </c>
@@ -4643,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>17</v>
       </c>
@@ -4672,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:17">
+    <row r="94" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>17</v>
       </c>
@@ -4701,7 +4711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:17">
+    <row r="95" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>17</v>
       </c>
@@ -4730,7 +4740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:17">
+    <row r="96" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>17</v>
       </c>
@@ -4759,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>17</v>
       </c>
@@ -4788,7 +4798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>17</v>
       </c>
@@ -4817,7 +4827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>17</v>
       </c>
@@ -4846,7 +4856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>17</v>
       </c>
@@ -4875,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>17</v>
       </c>
@@ -4904,7 +4914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>17</v>
       </c>
@@ -4933,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>17</v>
       </c>
@@ -4962,7 +4972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>17</v>
       </c>
@@ -4991,7 +5001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>17</v>
       </c>
@@ -5020,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>17</v>
       </c>
@@ -5049,7 +5059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>17</v>
       </c>
@@ -5078,7 +5088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>17</v>
       </c>
@@ -5107,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>17</v>
       </c>
@@ -5136,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>17</v>
       </c>
@@ -5165,7 +5175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>17</v>
       </c>
@@ -5194,7 +5204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>17</v>
       </c>
@@ -5223,7 +5233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>17</v>
       </c>
@@ -5252,7 +5262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>17</v>
       </c>
@@ -5281,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:17">
+    <row r="115" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>17</v>
       </c>
@@ -5310,7 +5320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>17</v>
       </c>
@@ -5339,7 +5349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:17">
+    <row r="117" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>17</v>
       </c>
@@ -5368,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:17">
+    <row r="118" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>140</v>
       </c>
@@ -5399,7 +5409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:17">
+    <row r="119" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>140</v>
       </c>
@@ -5430,7 +5440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:17">
+    <row r="120" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>140</v>
       </c>
@@ -5461,7 +5471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:17">
+    <row r="121" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>140</v>
       </c>
@@ -5492,7 +5502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:17">
+    <row r="122" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>140</v>
       </c>
@@ -5523,7 +5533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>140</v>
       </c>
@@ -5554,7 +5564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:17">
+    <row r="124" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>140</v>
       </c>
@@ -5585,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:17">
+    <row r="125" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>140</v>
       </c>
@@ -5616,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:17">
+    <row r="126" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>140</v>
       </c>
@@ -5647,7 +5657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:17">
+    <row r="127" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>140</v>
       </c>
@@ -5678,7 +5688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:17">
+    <row r="128" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>140</v>
       </c>
@@ -5709,7 +5719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:17">
+    <row r="129" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>140</v>
       </c>
@@ -5740,7 +5750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:17">
+    <row r="130" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>140</v>
       </c>
@@ -5771,7 +5781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:17">
+    <row r="131" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>140</v>
       </c>
@@ -5802,7 +5812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:17">
+    <row r="132" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>140</v>
       </c>
@@ -5833,7 +5843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:17">
+    <row r="133" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>140</v>
       </c>
@@ -5864,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:17">
+    <row r="134" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>140</v>
       </c>
@@ -5895,7 +5905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:17">
+    <row r="135" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>140</v>
       </c>
@@ -5926,7 +5936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:17">
+    <row r="136" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>140</v>
       </c>
@@ -5957,7 +5967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:17">
+    <row r="137" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>140</v>
       </c>
@@ -5988,7 +5998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>140</v>
       </c>
@@ -6019,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:17">
+    <row r="139" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>140</v>
       </c>
@@ -6050,7 +6060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:17">
+    <row r="140" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>140</v>
       </c>
@@ -6081,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:17">
+    <row r="141" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>140</v>
       </c>
@@ -6112,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:17">
+    <row r="142" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>140</v>
       </c>
@@ -6143,7 +6153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:17">
+    <row r="143" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>140</v>
       </c>
@@ -6174,7 +6184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:17">
+    <row r="144" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>140</v>
       </c>
@@ -6205,7 +6215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:17">
+    <row r="145" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>140</v>
       </c>
@@ -6236,7 +6246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:17">
+    <row r="146" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>140</v>
       </c>
@@ -6267,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:17">
+    <row r="147" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>140</v>
       </c>
@@ -6298,7 +6308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:17">
+    <row r="148" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>191</v>
       </c>
@@ -6327,7 +6337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:17">
+    <row r="149" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>191</v>
       </c>
@@ -6356,7 +6366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:17">
+    <row r="150" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>191</v>
       </c>
@@ -6385,7 +6395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:17">
+    <row r="151" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>191</v>
       </c>
@@ -6414,7 +6424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:17">
+    <row r="152" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>191</v>
       </c>
@@ -6443,7 +6453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:17">
+    <row r="153" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>191</v>
       </c>
@@ -6472,7 +6482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:17">
+    <row r="154" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>191</v>
       </c>
@@ -6501,7 +6511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:17">
+    <row r="155" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>191</v>
       </c>
@@ -6530,7 +6540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:17">
+    <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>191</v>
       </c>
@@ -6559,7 +6569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:17">
+    <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>191</v>
       </c>
@@ -6588,7 +6598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:17">
+    <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>191</v>
       </c>
@@ -6617,7 +6627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:17">
+    <row r="159" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>191</v>
       </c>
@@ -6646,7 +6656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:17">
+    <row r="160" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>191</v>
       </c>
@@ -6675,7 +6685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:17">
+    <row r="161" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>191</v>
       </c>
@@ -6704,7 +6714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:17">
+    <row r="162" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>191</v>
       </c>
@@ -6733,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:17">
+    <row r="163" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>191</v>
       </c>
@@ -6762,7 +6772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:17">
+    <row r="164" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>191</v>
       </c>
@@ -6791,7 +6801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:17">
+    <row r="165" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>191</v>
       </c>
@@ -6820,7 +6830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:17">
+    <row r="166" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>191</v>
       </c>
@@ -6849,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:17">
+    <row r="167" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>191</v>
       </c>
@@ -6878,7 +6888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:17">
+    <row r="168" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>191</v>
       </c>
@@ -6907,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>191</v>
       </c>
@@ -6936,7 +6946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>191</v>
       </c>
@@ -6965,7 +6975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:17">
+    <row r="171" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>191</v>
       </c>
@@ -6994,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:17">
+    <row r="172" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>191</v>
       </c>
@@ -7023,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:17">
+    <row r="173" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>191</v>
       </c>
@@ -7052,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:17">
+    <row r="174" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>191</v>
       </c>
@@ -7081,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:17">
+    <row r="175" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>191</v>
       </c>
@@ -7110,7 +7120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:17">
+    <row r="176" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>191</v>
       </c>
@@ -7139,7 +7149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:17">
+    <row r="177" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>191</v>
       </c>
@@ -7168,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:17">
+    <row r="178" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>191</v>
       </c>
@@ -7197,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:17">
+    <row r="179" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>191</v>
       </c>
@@ -7226,7 +7236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:17">
+    <row r="180" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>191</v>
       </c>
@@ -7255,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:17">
+    <row r="181" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>191</v>
       </c>
@@ -7284,7 +7294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:17">
+    <row r="182" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>191</v>
       </c>
@@ -7313,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:17">
+    <row r="183" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>191</v>
       </c>
@@ -7342,7 +7352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:17">
+    <row r="184" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>191</v>
       </c>
@@ -7371,7 +7381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:17">
+    <row r="185" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>191</v>
       </c>
@@ -7400,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:17">
+    <row r="186" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>191</v>
       </c>
@@ -7429,7 +7439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:17">
+    <row r="187" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>216</v>
       </c>
@@ -7458,7 +7468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:17">
+    <row r="188" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>216</v>
       </c>
@@ -7487,7 +7497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:17">
+    <row r="189" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>216</v>
       </c>
@@ -7516,7 +7526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:17">
+    <row r="190" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>216</v>
       </c>
@@ -7545,7 +7555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:17">
+    <row r="191" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>216</v>
       </c>
@@ -7574,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:17">
+    <row r="192" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>216</v>
       </c>
@@ -7603,7 +7613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:17">
+    <row r="193" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>216</v>
       </c>
@@ -7632,7 +7642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:17">
+    <row r="194" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>216</v>
       </c>
@@ -7661,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:17">
+    <row r="195" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>216</v>
       </c>
@@ -7690,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:17">
+    <row r="196" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>216</v>
       </c>
@@ -7719,7 +7729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:17">
+    <row r="197" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>216</v>
       </c>
@@ -7748,7 +7758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:17">
+    <row r="198" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>216</v>
       </c>
@@ -7777,7 +7787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:17">
+    <row r="199" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>216</v>
       </c>
@@ -7806,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:17">
+    <row r="200" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>216</v>
       </c>
@@ -7835,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:17">
+    <row r="201" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>216</v>
       </c>
@@ -7864,7 +7874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:17">
+    <row r="202" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>216</v>
       </c>
@@ -7893,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:17">
+    <row r="203" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>216</v>
       </c>
@@ -7922,7 +7932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:17">
+    <row r="204" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>216</v>
       </c>
@@ -7951,7 +7961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:17">
+    <row r="205" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>216</v>
       </c>
@@ -7980,7 +7990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:17">
+    <row r="206" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>216</v>
       </c>
@@ -8009,7 +8019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:17">
+    <row r="207" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>216</v>
       </c>
@@ -8038,7 +8048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:17">
+    <row r="208" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>216</v>
       </c>
@@ -8067,7 +8077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:17">
+    <row r="209" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
         <v>216</v>
       </c>
@@ -8096,7 +8106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:17">
+    <row r="210" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>216</v>
       </c>
@@ -8125,7 +8135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:17">
+    <row r="211" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
         <v>216</v>
       </c>
@@ -8154,7 +8164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:17">
+    <row r="212" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>216</v>
       </c>
@@ -8183,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:17">
+    <row r="213" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
         <v>216</v>
       </c>
@@ -8212,7 +8222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:17">
+    <row r="214" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>216</v>
       </c>
@@ -8241,7 +8251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:17">
+    <row r="215" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
         <v>216</v>
       </c>
@@ -8270,7 +8280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:17">
+    <row r="216" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>216</v>
       </c>
@@ -8299,7 +8309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:17">
+    <row r="217" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>216</v>
       </c>
@@ -8328,7 +8338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:17">
+    <row r="218" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>216</v>
       </c>
@@ -8357,7 +8367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:17">
+    <row r="219" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
         <v>216</v>
       </c>
@@ -8386,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:17">
+    <row r="220" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>216</v>
       </c>
@@ -8415,7 +8425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:17">
+    <row r="221" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
         <v>216</v>
       </c>
@@ -8444,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:17">
+    <row r="222" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>216</v>
       </c>
@@ -8473,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:17">
+    <row r="223" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>216</v>
       </c>
@@ -8502,7 +8512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:17">
+    <row r="224" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>216</v>
       </c>
@@ -8531,7 +8541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:17">
+    <row r="225" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
         <v>216</v>
       </c>
@@ -8560,7 +8570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:17">
+    <row r="226" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>216</v>
       </c>
@@ -8589,7 +8599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:17">
+    <row r="227" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>216</v>
       </c>
@@ -8618,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:17">
+    <row r="228" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>216</v>
       </c>
@@ -8647,7 +8657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:17">
+    <row r="229" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
         <v>216</v>
       </c>
@@ -8676,7 +8686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17">
+    <row r="230" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>216</v>
       </c>
@@ -8705,7 +8715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17">
+    <row r="231" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
         <v>216</v>
       </c>
@@ -8734,7 +8744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17">
+    <row r="232" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>216</v>
       </c>
@@ -8763,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17">
+    <row r="233" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
         <v>216</v>
       </c>
@@ -8792,7 +8802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17">
+    <row r="234" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>216</v>
       </c>
@@ -8821,7 +8831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17">
+    <row r="235" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
         <v>216</v>
       </c>
@@ -8850,7 +8860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17">
+    <row r="236" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>216</v>
       </c>
@@ -8879,7 +8889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17">
+    <row r="237" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>216</v>
       </c>
@@ -8908,7 +8918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17">
+    <row r="238" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>216</v>
       </c>
@@ -8937,7 +8947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:17">
+    <row r="239" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>216</v>
       </c>
@@ -8966,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:17">
+    <row r="240" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>216</v>
       </c>
@@ -8995,7 +9005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:17">
+    <row r="241" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>216</v>
       </c>
@@ -9024,7 +9034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:17">
+    <row r="242" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>236</v>
       </c>
@@ -9055,7 +9065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:17">
+    <row r="243" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
         <v>236</v>
       </c>
@@ -9086,7 +9096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:17">
+    <row r="244" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>236</v>
       </c>
@@ -9117,7 +9127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:17">
+    <row r="245" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>236</v>
       </c>
@@ -9148,7 +9158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:17">
+    <row r="246" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>236</v>
       </c>
@@ -9179,7 +9189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:17">
+    <row r="247" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>236</v>
       </c>
@@ -9210,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:17">
+    <row r="248" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>236</v>
       </c>
@@ -9241,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:17">
+    <row r="249" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>236</v>
       </c>
@@ -9272,7 +9282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:17">
+    <row r="250" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>236</v>
       </c>
@@ -9303,7 +9313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:17">
+    <row r="251" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>236</v>
       </c>
@@ -9334,7 +9344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:17">
+    <row r="252" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>236</v>
       </c>
@@ -9365,7 +9375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:17">
+    <row r="253" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>236</v>
       </c>
@@ -9396,7 +9406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:17">
+    <row r="254" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>236</v>
       </c>
@@ -9427,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:17">
+    <row r="255" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>236</v>
       </c>
@@ -9458,7 +9468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:17">
+    <row r="256" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>236</v>
       </c>
@@ -9489,7 +9499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17">
+    <row r="257" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>236</v>
       </c>
@@ -9520,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:17">
+    <row r="258" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>236</v>
       </c>
@@ -9551,7 +9561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:17">
+    <row r="259" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
         <v>236</v>
       </c>
@@ -9582,7 +9592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:17">
+    <row r="260" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>236</v>
       </c>
@@ -9613,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:17">
+    <row r="261" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>236</v>
       </c>
@@ -9644,7 +9654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:17">
+    <row r="262" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>236</v>
       </c>
@@ -9675,7 +9685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:17">
+    <row r="263" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>236</v>
       </c>
@@ -9706,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17">
+    <row r="264" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>236</v>
       </c>
@@ -9737,7 +9747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17">
+    <row r="265" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>236</v>
       </c>
@@ -9768,7 +9778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17">
+    <row r="266" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>236</v>
       </c>
@@ -9799,7 +9809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17">
+    <row r="267" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>236</v>
       </c>
@@ -9830,7 +9840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17">
+    <row r="268" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>236</v>
       </c>
@@ -9861,7 +9871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:17">
+    <row r="269" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>236</v>
       </c>
@@ -9892,7 +9902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17">
+    <row r="270" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>236</v>
       </c>
@@ -9923,7 +9933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17">
+    <row r="271" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>236</v>
       </c>
@@ -9954,7 +9964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17">
+    <row r="272" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>236</v>
       </c>
@@ -9985,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:17">
+    <row r="273" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>236</v>
       </c>
@@ -10016,7 +10026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:17">
+    <row r="274" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>236</v>
       </c>
@@ -10047,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:17">
+    <row r="275" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>236</v>
       </c>
@@ -10078,7 +10088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:17">
+    <row r="276" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>236</v>
       </c>
@@ -10109,7 +10119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:17">
+    <row r="277" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>236</v>
       </c>
@@ -10140,7 +10150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:17">
+    <row r="278" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
         <v>236</v>
       </c>
@@ -10171,7 +10181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:17">
+    <row r="279" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>236</v>
       </c>
@@ -10202,7 +10212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:17">
+    <row r="280" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
         <v>236</v>
       </c>
@@ -10233,7 +10243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:17">
+    <row r="281" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>236</v>
       </c>
@@ -10264,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:17">
+    <row r="282" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>236</v>
       </c>
@@ -10295,7 +10305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:17">
+    <row r="283" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
         <v>236</v>
       </c>
@@ -10326,7 +10336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:17">
+    <row r="284" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
         <v>236</v>
       </c>
@@ -10357,7 +10367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:17">
+    <row r="285" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
         <v>337</v>
       </c>
@@ -10390,7 +10400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:17">
+    <row r="286" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
         <v>337</v>
       </c>
@@ -10423,7 +10433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:17">
+    <row r="287" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>337</v>
       </c>
@@ -10456,7 +10466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:17">
+    <row r="288" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
         <v>337</v>
       </c>
@@ -10489,7 +10499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:17">
+    <row r="289" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
         <v>337</v>
       </c>
@@ -10522,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:17">
+    <row r="290" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
         <v>337</v>
       </c>
@@ -10555,7 +10565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:17">
+    <row r="291" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
         <v>337</v>
       </c>
@@ -10588,7 +10598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:17">
+    <row r="292" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>337</v>
       </c>
@@ -10621,7 +10631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:17">
+    <row r="293" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
         <v>337</v>
       </c>
@@ -10654,7 +10664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:17">
+    <row r="294" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>337</v>
       </c>
@@ -10687,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:17">
+    <row r="295" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
         <v>337</v>
       </c>
@@ -10720,15 +10730,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:17">
+    <row r="296" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
         <v>337</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C296" s="2" t="s">
-        <v>372</v>
+      <c r="C296" s="9" t="s">
+        <v>502</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
@@ -10737,10 +10747,10 @@
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
       <c r="J296" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="K296" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="K296" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="L296" s="2" t="s">
         <v>279</v>
@@ -10753,7 +10763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:17">
+    <row r="297" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
         <v>337</v>
       </c>
@@ -10761,7 +10771,7 @@
         <v>62</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
@@ -10770,13 +10780,13 @@
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K297" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="K297" s="2" t="s">
+      <c r="L297" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="L297" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="M297" s="2"/>
       <c r="N297" s="2"/>
@@ -10786,7 +10796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:17">
+    <row r="298" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
         <v>337</v>
       </c>
@@ -10794,7 +10804,7 @@
         <v>62</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
@@ -10803,13 +10813,13 @@
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
       <c r="J298" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="K298" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="L298" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="K298" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="L298" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="M298" s="2"/>
       <c r="N298" s="2"/>
@@ -10819,7 +10829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:17">
+    <row r="299" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
         <v>337</v>
       </c>
@@ -10827,7 +10837,7 @@
         <v>62</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
@@ -10836,7 +10846,7 @@
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K299" s="2" t="s">
         <v>371</v>
@@ -10852,7 +10862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:17">
+    <row r="300" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
         <v>337</v>
       </c>
@@ -10860,7 +10870,7 @@
         <v>62</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
@@ -10869,10 +10879,10 @@
       <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="J300" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K300" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="K300" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="L300" s="2" t="s">
         <v>129</v>
@@ -10885,7 +10895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:17">
+    <row r="301" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
         <v>337</v>
       </c>
@@ -10893,7 +10903,7 @@
         <v>62</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
@@ -10902,13 +10912,13 @@
       <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="J301" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K301" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="K301" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="L301" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M301" s="2"/>
       <c r="N301" s="2"/>
@@ -10918,7 +10928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:17">
+    <row r="302" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
         <v>337</v>
       </c>
@@ -10926,7 +10936,7 @@
         <v>62</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" s="2"/>
@@ -10935,13 +10945,13 @@
       <c r="H302" s="2"/>
       <c r="I302" s="2"/>
       <c r="J302" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K302" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="L302" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="K302" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="L302" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
@@ -10951,7 +10961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:17">
+    <row r="303" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
         <v>337</v>
       </c>
@@ -10959,7 +10969,7 @@
         <v>62</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
@@ -10968,10 +10978,10 @@
       <c r="H303" s="2"/>
       <c r="I303" s="2"/>
       <c r="J303" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="K303" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="K303" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="L303" s="2" t="s">
         <v>207</v>
@@ -10984,7 +10994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:17">
+    <row r="304" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
         <v>337</v>
       </c>
@@ -10992,7 +11002,7 @@
         <v>62</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" s="2"/>
@@ -11001,10 +11011,10 @@
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="K304" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="K304" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="L304" s="2" t="s">
         <v>70</v>
@@ -11017,7 +11027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:17">
+    <row r="305" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
         <v>337</v>
       </c>
@@ -11025,7 +11035,7 @@
         <v>103</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
@@ -11034,13 +11044,13 @@
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
       <c r="J305" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K305" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="K305" s="2" t="s">
+      <c r="L305" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="L305" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
@@ -11050,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:17">
+    <row r="306" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
         <v>337</v>
       </c>
@@ -11058,7 +11068,7 @@
         <v>103</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" s="2"/>
@@ -11067,13 +11077,13 @@
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K306" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="K306" s="2" t="s">
+      <c r="L306" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="L306" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
@@ -11083,7 +11093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:17">
+    <row r="307" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
         <v>337</v>
       </c>
@@ -11091,7 +11101,7 @@
         <v>103</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" s="2"/>
@@ -11100,13 +11110,13 @@
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="J307" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K307" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="K307" s="2" t="s">
+      <c r="L307" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="L307" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
@@ -11116,7 +11126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:17">
+    <row r="308" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
         <v>337</v>
       </c>
@@ -11124,7 +11134,7 @@
         <v>103</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" s="2"/>
@@ -11133,10 +11143,10 @@
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K308" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="K308" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="L308" s="2" t="s">
         <v>34</v>
@@ -11149,7 +11159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:17">
+    <row r="309" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>337</v>
       </c>
@@ -11157,7 +11167,7 @@
         <v>103</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" s="2"/>
@@ -11166,13 +11176,13 @@
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="J309" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K309" s="2" t="s">
         <v>365</v>
       </c>
       <c r="L309" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M309" s="2"/>
       <c r="N309" s="2"/>
@@ -11182,7 +11192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:17">
+    <row r="310" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
         <v>337</v>
       </c>
@@ -11190,7 +11200,7 @@
         <v>103</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
@@ -11199,13 +11209,13 @@
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="J310" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="K310" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="K310" s="2" t="s">
+      <c r="L310" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="L310" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="M310" s="2"/>
       <c r="N310" s="2"/>
@@ -11215,7 +11225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:17">
+    <row r="311" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
         <v>337</v>
       </c>
@@ -11223,7 +11233,7 @@
         <v>103</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
@@ -11232,13 +11242,13 @@
       <c r="H311" s="2"/>
       <c r="I311" s="2"/>
       <c r="J311" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K311" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="K311" s="2" t="s">
+      <c r="L311" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="L311" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="M311" s="2"/>
       <c r="N311" s="2"/>
@@ -11248,7 +11258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:17">
+    <row r="312" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
         <v>337</v>
       </c>
@@ -11256,7 +11266,7 @@
         <v>103</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
@@ -11265,13 +11275,13 @@
       <c r="H312" s="2"/>
       <c r="I312" s="2"/>
       <c r="J312" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K312" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="K312" s="2" t="s">
+      <c r="L312" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="L312" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
@@ -11281,7 +11291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:17">
+    <row r="313" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
         <v>337</v>
       </c>
@@ -11289,7 +11299,7 @@
         <v>103</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" s="2"/>
@@ -11298,13 +11308,13 @@
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
       <c r="J313" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="K313" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="K313" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="L313" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
@@ -11314,7 +11324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:17">
+    <row r="314" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
         <v>337</v>
       </c>
@@ -11322,7 +11332,7 @@
         <v>103</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
@@ -11331,10 +11341,10 @@
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
       <c r="J314" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K314" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="K314" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="L314" s="2" t="s">
         <v>287</v>
@@ -11347,15 +11357,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:17">
+    <row r="315" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B315" s="2" t="s">
+      <c r="C315" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" s="2"/>
@@ -11367,10 +11377,10 @@
       <c r="K315" s="2"/>
       <c r="L315" s="2"/>
       <c r="M315" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N315" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="N315" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="O315" s="2"/>
       <c r="P315" s="2"/>
@@ -11378,15 +11388,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:17">
+    <row r="316" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C316" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" s="2"/>
@@ -11398,10 +11408,10 @@
       <c r="K316" s="2"/>
       <c r="L316" s="2"/>
       <c r="M316" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N316" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="N316" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="O316" s="2"/>
       <c r="P316" s="2"/>
@@ -11409,15 +11419,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:17">
+    <row r="317" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C317" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" s="2"/>
@@ -11429,10 +11439,10 @@
       <c r="K317" s="2"/>
       <c r="L317" s="2"/>
       <c r="M317" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="N317" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="N317" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="O317" s="2"/>
       <c r="P317" s="2"/>
@@ -11440,15 +11450,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:17">
+    <row r="318" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C318" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" s="2"/>
@@ -11460,10 +11470,10 @@
       <c r="K318" s="2"/>
       <c r="L318" s="2"/>
       <c r="M318" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="N318" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="N318" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="O318" s="2"/>
       <c r="P318" s="2"/>
@@ -11471,15 +11481,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:17">
+    <row r="319" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B319" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B319" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C319" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" s="2"/>
@@ -11491,10 +11501,10 @@
       <c r="K319" s="2"/>
       <c r="L319" s="2"/>
       <c r="M319" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N319" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O319" s="2"/>
       <c r="P319" s="2"/>
@@ -11502,15 +11512,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:17">
+    <row r="320" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B320" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C320" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" s="2"/>
@@ -11522,10 +11532,10 @@
       <c r="K320" s="2"/>
       <c r="L320" s="2"/>
       <c r="M320" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N320" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O320" s="2"/>
       <c r="P320" s="2"/>
@@ -11533,15 +11543,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:17">
+    <row r="321" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B321" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C321" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" s="2"/>
@@ -11553,10 +11563,10 @@
       <c r="K321" s="2"/>
       <c r="L321" s="2"/>
       <c r="M321" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="N321" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="N321" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="O321" s="2"/>
       <c r="P321" s="2"/>
@@ -11564,15 +11574,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:17">
+    <row r="322" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B322" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B322" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C322" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" s="2"/>
@@ -11584,7 +11594,7 @@
       <c r="K322" s="2"/>
       <c r="L322" s="2"/>
       <c r="M322" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N322" s="2"/>
       <c r="O322" s="2"/>
@@ -11593,15 +11603,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:17">
+    <row r="323" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B323" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B323" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C323" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
@@ -11613,7 +11623,7 @@
       <c r="K323" s="2"/>
       <c r="L323" s="2"/>
       <c r="M323" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N323" s="2"/>
       <c r="O323" s="2"/>
@@ -11622,15 +11632,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:17">
+    <row r="324" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="C324" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" s="2"/>
@@ -11642,7 +11652,7 @@
       <c r="K324" s="2"/>
       <c r="L324" s="2"/>
       <c r="M324" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N324" s="2"/>
       <c r="O324" s="2"/>
@@ -11651,9 +11661,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:17">
+    <row r="325" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>18</v>
@@ -11680,9 +11690,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:17">
+    <row r="326" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>18</v>
@@ -11709,9 +11719,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:17">
+    <row r="327" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>18</v>
@@ -11738,9 +11748,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:17">
+    <row r="328" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>18</v>
@@ -11767,9 +11777,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:17">
+    <row r="329" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>18</v>
@@ -11796,9 +11806,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:17">
+    <row r="330" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>18</v>
@@ -11825,9 +11835,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:17">
+    <row r="331" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>18</v>
@@ -11854,9 +11864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:17">
+    <row r="332" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>18</v>
@@ -11883,9 +11893,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:17">
+    <row r="333" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>18</v>
@@ -11912,9 +11922,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:17">
+    <row r="334" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>18</v>
@@ -11941,9 +11951,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:17">
+    <row r="335" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>62</v>
@@ -11970,9 +11980,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:17">
+    <row r="336" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>62</v>
@@ -11999,15 +12009,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:17">
+    <row r="337" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" s="2"/>
@@ -12028,9 +12038,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:17">
+    <row r="338" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>62</v>
@@ -12057,9 +12067,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:17">
+    <row r="339" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>62</v>
@@ -12086,9 +12096,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:17">
+    <row r="340" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>62</v>
@@ -12115,15 +12125,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:17">
+    <row r="341" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" s="2"/>
@@ -12144,15 +12154,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:17">
+    <row r="342" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" s="2"/>
@@ -12173,9 +12183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:17">
+    <row r="343" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>62</v>
@@ -12202,9 +12212,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:17">
+    <row r="344" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>62</v>
@@ -12231,15 +12241,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:17">
+    <row r="345" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" s="2"/>
@@ -12260,15 +12270,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:17">
+    <row r="346" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" s="2"/>
@@ -12289,15 +12299,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:17">
+    <row r="347" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
@@ -12318,15 +12328,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:17">
+    <row r="348" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" s="2"/>
@@ -12347,15 +12357,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:17">
+    <row r="349" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
@@ -12376,15 +12386,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:17">
+    <row r="350" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
@@ -12405,15 +12415,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:17">
+    <row r="351" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
@@ -12434,15 +12444,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:17">
+    <row r="352" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" s="2"/>
@@ -12463,15 +12473,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:17">
+    <row r="353" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
@@ -12492,15 +12502,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:17">
+    <row r="354" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" s="2"/>
@@ -12521,15 +12531,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:17">
+    <row r="355" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" s="2"/>
@@ -12544,21 +12554,21 @@
       <c r="N355" s="2"/>
       <c r="O355" s="2"/>
       <c r="P355" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q355" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A356" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="Q355" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:17">
-      <c r="A356" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" s="2"/>
@@ -12573,21 +12583,21 @@
       <c r="N356" s="2"/>
       <c r="O356" s="2"/>
       <c r="P356" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q356" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A357" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="Q356" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:17">
-      <c r="A357" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" s="2"/>
@@ -12602,21 +12612,21 @@
       <c r="N357" s="2"/>
       <c r="O357" s="2"/>
       <c r="P357" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q357" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A358" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C358" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="Q357" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="1:17">
-      <c r="A358" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C358" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" s="2"/>
@@ -12631,21 +12641,21 @@
       <c r="N358" s="2"/>
       <c r="O358" s="2"/>
       <c r="P358" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q358" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:17">
+    <row r="359" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" s="2"/>
@@ -12660,21 +12670,21 @@
       <c r="N359" s="2"/>
       <c r="O359" s="2"/>
       <c r="P359" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q359" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:17">
+    <row r="360" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" s="2"/>
@@ -12689,21 +12699,21 @@
       <c r="N360" s="2"/>
       <c r="O360" s="2"/>
       <c r="P360" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q360" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:17">
+    <row r="361" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" s="2"/>
@@ -12718,21 +12728,21 @@
       <c r="N361" s="2"/>
       <c r="O361" s="2"/>
       <c r="P361" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q361" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:17">
+    <row r="362" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" s="2"/>
@@ -12747,21 +12757,21 @@
       <c r="N362" s="2"/>
       <c r="O362" s="2"/>
       <c r="P362" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q362" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:17">
+    <row r="363" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
@@ -12776,21 +12786,21 @@
       <c r="N363" s="2"/>
       <c r="O363" s="2"/>
       <c r="P363" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q363" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:17">
+    <row r="364" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A364" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" s="2"/>
@@ -12805,21 +12815,21 @@
       <c r="N364" s="2"/>
       <c r="O364" s="2"/>
       <c r="P364" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q364" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:17">
+    <row r="365" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
@@ -12834,21 +12844,21 @@
       <c r="N365" s="2"/>
       <c r="O365" s="2"/>
       <c r="P365" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q365" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:17">
+    <row r="366" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" s="2"/>
@@ -12863,21 +12873,21 @@
       <c r="N366" s="2"/>
       <c r="O366" s="2"/>
       <c r="P366" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q366" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:17">
+    <row r="367" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" s="2"/>
@@ -12892,21 +12902,21 @@
       <c r="N367" s="2"/>
       <c r="O367" s="2"/>
       <c r="P367" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q367" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:17">
+    <row r="368" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" s="2"/>
@@ -12921,21 +12931,21 @@
       <c r="N368" s="2"/>
       <c r="O368" s="2"/>
       <c r="P368" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q368" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:17">
+    <row r="369" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" s="2"/>
@@ -12950,21 +12960,21 @@
       <c r="N369" s="2"/>
       <c r="O369" s="2"/>
       <c r="P369" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q369" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:17">
+    <row r="370" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" s="2"/>
@@ -12979,117 +12989,81 @@
       <c r="N370" s="2"/>
       <c r="O370" s="2"/>
       <c r="P370" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q370" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:17"/>
-    <row r="372" spans="1:17"/>
-    <row r="373" spans="1:17"/>
-    <row r="374" spans="1:17"/>
-    <row r="375" spans="1:17"/>
-    <row r="376" spans="1:17"/>
-    <row r="377" spans="1:17"/>
-    <row r="378" spans="1:17"/>
-    <row r="379" spans="1:17"/>
-    <row r="380" spans="1:17"/>
-    <row r="381" spans="1:17"/>
-    <row r="382" spans="1:17"/>
-    <row r="383" spans="1:17"/>
-    <row r="384" spans="1:17"/>
-    <row r="385" spans="1:17"/>
-    <row r="386" spans="1:17"/>
-    <row r="387" spans="1:17"/>
-    <row r="388" spans="1:17"/>
-    <row r="389" spans="1:17"/>
-    <row r="390" spans="1:17"/>
-    <row r="391" spans="1:17"/>
-    <row r="392" spans="1:17"/>
-    <row r="393" spans="1:17"/>
-    <row r="394" spans="1:17"/>
-    <row r="395" spans="1:17"/>
-    <row r="396" spans="1:17"/>
-    <row r="397" spans="1:17"/>
-    <row r="398" spans="1:17"/>
-    <row r="399" spans="1:17"/>
-    <row r="400" spans="1:17"/>
   </sheetData>
-  <autoFilter ref="A1:Q370"/>
-  <dataValidations count="4">
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A2:A400">
+  <autoFilter ref="A1:Q370" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <dataValidations count="3">
+    <dataValidation type="list" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"deutsch_artikel,deutsch_reime,deutsch_gross_klein,deutsch_wortarten,deutsch_plural,deutsch_rechtschreibung,deutsch_zeitformen,deutsch_silben,deutsch_satzzeichen"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B2:B400">
+    <dataValidation type="list" sqref="B2:B400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"easy,medium,hard,all"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F2:F400">
-      <formula1>"0,1,true,false,ja,nein,yes,no"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="Q2:Q400">
+    <dataValidation type="list" errorStyle="information" allowBlank="1" sqref="F2:F400 Q2:Q400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"0,1,true,false,ja,nein,yes,no"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="true" style="0"/>
-    <col min="2" max="2" width="18" customWidth="true" style="0"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B1" s="6"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>481</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
-        <v>482</v>
       </c>
       <c r="B4" s="3">
         <v>369</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B5" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -13097,7 +13071,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>191</v>
       </c>
@@ -13105,7 +13079,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>236</v>
       </c>
@@ -13113,7 +13087,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>337</v>
       </c>
@@ -13121,7 +13095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -13129,23 +13103,23 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B15">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>216</v>
       </c>
@@ -13153,28 +13127,28 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -13182,7 +13156,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -13190,7 +13164,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>62</v>
       </c>
@@ -13199,261 +13173,256 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="true" style="0"/>
-    <col min="2" max="2" width="96" customWidth="true" style="0"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="B1" s="6"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="B2" s="6"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="6" t="s">
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="6" t="s">
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="6" t="s">
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B18" s="6" t="s">
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B19" s="6" t="s">
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="B21" s="6" t="s">
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="B22" s="6" t="s">
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>